--- a/Advexcel/Excel Text Functions - Stu.xlsx
+++ b/Advexcel/Excel Text Functions - Stu.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karan/Desktop/EXCEL ITVEDANT/Advexcel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00D825CC-730C-9048-84E1-B7173BA2768E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60F8F09D-677D-4644-A4D6-F68F4DB4A019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="2" xr2:uid="{DD48EB59-D422-440A-B3D8-B7024E933AC0}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="1" xr2:uid="{DD48EB59-D422-440A-B3D8-B7024E933AC0}"/>
   </bookViews>
   <sheets>
     <sheet name="Text to Columns" sheetId="4" r:id="rId1"/>
@@ -1050,7 +1050,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1410,6 +1410,28 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{25653891-01DF-1045-8EAF-DBAA0701CCA1}">
+  <we:reference id="wa200010215" version="2.0.0.1" store="en-GB" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="wa200010215" version="2.0.0.1" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="bps.codex_control.document_id" value="&quot;985d5d13-095f-4578-8269-f85627b8afff&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9F809E7-4C3C-4662-93E5-538B26B063F3}">
   <sheetPr codeName="Sheet21"/>
@@ -24372,7 +24394,7 @@
         <v>279</v>
       </c>
       <c r="B6" t="str">
-        <f>LEFT(A6,FIND("@",A6)-1)</f>
+        <f t="shared" ref="B6:B11" si="0">LEFT(A6,FIND("@",A6)-1)</f>
         <v>amit</v>
       </c>
       <c r="C6" t="str">
@@ -24385,11 +24407,11 @@
         <v>280</v>
       </c>
       <c r="B7" t="str">
-        <f>LEFT(A7,FIND("@",A7)-1)</f>
+        <f t="shared" si="0"/>
         <v>himanshu</v>
       </c>
       <c r="C7" t="str">
-        <f t="shared" ref="C7:C11" si="0">MID(A7,FIND("@",A7)+1,FIND(".",A7)-FIND("@",A7)-1)</f>
+        <f t="shared" ref="C7:C11" si="1">MID(A7,FIND("@",A7)+1,FIND(".",A7)-FIND("@",A7)-1)</f>
         <v>gmail</v>
       </c>
     </row>
@@ -24398,11 +24420,11 @@
         <v>281</v>
       </c>
       <c r="B8" t="str">
-        <f>LEFT(A8,FIND("@",A8)-1)</f>
+        <f t="shared" si="0"/>
         <v>om</v>
       </c>
       <c r="C8" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>gmail</v>
       </c>
       <c r="G8" t="s">
@@ -24414,11 +24436,11 @@
         <v>295</v>
       </c>
       <c r="B9" t="str">
-        <f>LEFT(A9,FIND("@",A9)-1)</f>
+        <f t="shared" si="0"/>
         <v>pooja</v>
       </c>
       <c r="C9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>microsoft</v>
       </c>
     </row>
@@ -24427,11 +24449,11 @@
         <v>296</v>
       </c>
       <c r="B10" t="str">
-        <f>LEFT(A10,FIND("@",A10)-1)</f>
+        <f t="shared" si="0"/>
         <v>nitin</v>
       </c>
       <c r="C10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>rediffmail</v>
       </c>
     </row>
@@ -24440,11 +24462,11 @@
         <v>297</v>
       </c>
       <c r="B11" t="str">
-        <f>LEFT(A11,FIND("@",A11)-1)</f>
+        <f t="shared" si="0"/>
         <v>rohan</v>
       </c>
       <c r="C11" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>outlook</v>
       </c>
     </row>
@@ -24456,7 +24478,7 @@
         <v>284</v>
       </c>
       <c r="C13" t="e">
-        <f t="shared" ref="C13:C14" si="1">MID(A13,FIND("@",A13),6)</f>
+        <f t="shared" ref="C13:C14" si="2">MID(A13,FIND("@",A13),6)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -24469,7 +24491,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="C14" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -24516,11 +24538,11 @@
         <v>9766641822</v>
       </c>
       <c r="B18" s="6" t="str">
-        <f t="shared" ref="B18:B19" si="2">REPLACE(A18,1,6,"xxxxxx")</f>
+        <f t="shared" ref="B18:B19" si="3">REPLACE(A18,1,6,"xxxxxx")</f>
         <v>xxxxxx1822</v>
       </c>
       <c r="C18" s="6" t="str">
-        <f t="shared" ref="C18:C19" si="3">REPLACE(A18,7,4,"xxxx")</f>
+        <f t="shared" ref="C18:C19" si="4">REPLACE(A18,7,4,"xxxx")</f>
         <v>976664xxxx</v>
       </c>
     </row>
@@ -24529,11 +24551,11 @@
         <v>9923712793</v>
       </c>
       <c r="B19" s="6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>xxxxxx2793</v>
       </c>
       <c r="C19" s="6" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>992371xxxx</v>
       </c>
     </row>
@@ -24610,15 +24632,15 @@
         <v>29</v>
       </c>
       <c r="B29" s="6" t="str">
-        <f t="shared" ref="B29:B37" si="4">LEFT(A29,FIND(",",A29)-1)</f>
+        <f t="shared" ref="B29:B37" si="5">LEFT(A29,FIND(",",A29)-1)</f>
         <v>Glendale</v>
       </c>
       <c r="C29" s="6" t="str">
-        <f t="shared" ref="C29:C37" si="5">MID(A29,FIND(",",A29)+2,LEN(A29)-FIND(",",A29)-8)</f>
+        <f t="shared" ref="C29:C37" si="6">MID(A29,FIND(",",A29)+2,LEN(A29)-FIND(",",A29)-8)</f>
         <v>Arizona</v>
       </c>
       <c r="D29" s="6" t="str">
-        <f t="shared" ref="D29:D37" si="6">RIGHT(A29,5)</f>
+        <f t="shared" ref="D29:D37" si="7">RIGHT(A29,5)</f>
         <v>85302</v>
       </c>
       <c r="E29">
@@ -24626,7 +24648,7 @@
         <v>8</v>
       </c>
       <c r="F29" t="str">
-        <f t="shared" ref="F29:F37" si="7">MID(A29,FIND(" ",A29)+1,FIND(" ",A29,12)-FIND(" ",A29))</f>
+        <f t="shared" ref="F29:F37" si="8">MID(A29,FIND(" ",A29)+1,FIND(" ",A29,12)-FIND(" ",A29))</f>
         <v xml:space="preserve">Arizona </v>
       </c>
     </row>
@@ -24635,15 +24657,15 @@
         <v>30</v>
       </c>
       <c r="B30" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Mesa</v>
       </c>
       <c r="C30" s="6" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Arizona</v>
       </c>
       <c r="D30" s="6" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>85201</v>
       </c>
       <c r="E30">
@@ -24651,7 +24673,7 @@
         <v>10</v>
       </c>
       <c r="F30" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">Arizona </v>
       </c>
     </row>
@@ -24660,19 +24682,19 @@
         <v>31</v>
       </c>
       <c r="B31" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Peoria</v>
       </c>
       <c r="C31" s="6" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Arizona</v>
       </c>
       <c r="D31" s="6" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>85381</v>
       </c>
       <c r="F31" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">Arizona </v>
       </c>
     </row>
@@ -24681,19 +24703,19 @@
         <v>34</v>
       </c>
       <c r="B32" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Tempe</v>
       </c>
       <c r="C32" s="6" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Arizona</v>
       </c>
       <c r="D32" s="6" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>85282</v>
       </c>
       <c r="F32" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">Arizona </v>
       </c>
     </row>
@@ -24702,19 +24724,19 @@
         <v>35</v>
       </c>
       <c r="B33" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Tucson</v>
       </c>
       <c r="C33" s="6" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Arizona</v>
       </c>
       <c r="D33" s="6" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>85726</v>
       </c>
       <c r="F33" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">Arizona </v>
       </c>
     </row>
@@ -24723,19 +24745,19 @@
         <v>36</v>
       </c>
       <c r="B34" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Little Rock</v>
       </c>
       <c r="C34" s="6" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Arkansas</v>
       </c>
       <c r="D34" s="6" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>72202</v>
       </c>
       <c r="F34" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">Rock, </v>
       </c>
     </row>
@@ -24744,19 +24766,19 @@
         <v>37</v>
       </c>
       <c r="B35" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Anaheim</v>
       </c>
       <c r="C35" s="6" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>California</v>
       </c>
       <c r="D35" s="6" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>92803</v>
       </c>
       <c r="F35" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">California </v>
       </c>
     </row>
@@ -24765,19 +24787,19 @@
         <v>38</v>
       </c>
       <c r="B36" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Antioch</v>
       </c>
       <c r="C36" s="6" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>California</v>
       </c>
       <c r="D36" s="6" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>94509</v>
       </c>
       <c r="F36" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v xml:space="preserve">California </v>
       </c>
     </row>
@@ -24786,19 +24808,19 @@
         <v>39</v>
       </c>
       <c r="B37" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Bakersfield</v>
       </c>
       <c r="C37" s="6" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>California</v>
       </c>
       <c r="D37" s="6" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>93380</v>
       </c>
       <c r="F37" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
